--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud and Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320c1faffbfddbde</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98b55439904bef</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d675a6d5bcaeac</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=45e9be9ee46290f1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=4a365abdf57475b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=230910c469de2d76</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c24bfaec7c9da6f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=451f37250ad0deac</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=b95355c1d74b312f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>20.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3843d714f27ed59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=78c7318f2c1862c3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=91f462652eeb816d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=7700cc8c2471209c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=9808c47b5c4db28f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=7306270caf1d6506</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a47090faeee0433</t>
         </is>
       </c>
     </row>
@@ -998,20 +998,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=58422662e905e73b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>20.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=51a7cffbc3607a3c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>19.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud and Data Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>18.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=320c1faffbfddbde</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Manus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Augusta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Navitas</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Platform Engineer - CDE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,54 +1861,54 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hanvok Group LLC</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=215add5ff61dcad5</t>
+          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=13e82084d20e9979</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f4b90394ec3735</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Development Engineer (AI &amp; ML)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, ECS, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe7c58c72e83874</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Navitas</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=010939cb7a520dc3</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,40 +4276,1335 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>SQL/Power BI Developer</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Intellibee Inc</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Raleigh, NC, US USA</t>
         </is>
       </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G148"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Digipulse Technologies Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Kinesis, Athena, S3, SQS, SNS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98b55439904bef</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb5051399e08706</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d675a6d5bcaeac</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98b55439904bef</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e9be9ee46290f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d675a6d5bcaeac</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a365abdf57475b3</t>
+          <t>https://www.indeed.com/viewjob?jk=45e9be9ee46290f1</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230910c469de2d76</t>
+          <t>https://www.indeed.com/viewjob?jk=4a365abdf57475b3</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c24bfaec7c9da6f</t>
+          <t>https://www.indeed.com/viewjob?jk=230910c469de2d76</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451f37250ad0deac</t>
+          <t>https://www.indeed.com/viewjob?jk=7c24bfaec7c9da6f</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95355c1d74b312f</t>
+          <t>https://www.indeed.com/viewjob?jk=451f37250ad0deac</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3843d714f27ed59</t>
+          <t>https://www.indeed.com/viewjob?jk=b95355c1d74b312f</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c7318f2c1862c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3843d714f27ed59</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f462652eeb816d</t>
+          <t>https://www.indeed.com/viewjob?jk=78c7318f2c1862c3</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7700cc8c2471209c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f462652eeb816d</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9808c47b5c4db28f</t>
+          <t>https://www.indeed.com/viewjob?jk=7700cc8c2471209c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7306270caf1d6506</t>
+          <t>https://www.indeed.com/viewjob?jk=9808c47b5c4db28f</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a47090faeee0433</t>
+          <t>https://www.indeed.com/viewjob?jk=7306270caf1d6506</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58422662e905e73b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a47090faeee0433</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a7cffbc3607a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=58422662e905e73b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,15 +1073,15 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
+          <t>https://www.indeed.com/viewjob?jk=51a7cffbc3607a3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud and Data Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320c1faffbfddbde</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Cloud and Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Technology Ventures</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=320c1faffbfddbde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Manus</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Augusta, GA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Event Hubs, Medallion Architecture, Spark, PySpark, Kafka, Kafka Connect, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7422317da3cb8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Platform Engineer - CDE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,19 +1896,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e82084d20e9979</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f4b90394ec3735</t>
+          <t>https://www.indeed.com/viewjob?jk=13e82084d20e9979</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f4b90394ec3735</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI &amp; ML)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Software Development Engineer (AI &amp; ML)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Navitas</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Navitas</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010939cb7a520dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=010939cb7a520dc3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,59 +2911,59 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,40 +5571,75 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
           <t>SQL/Power BI Developer</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>Intellibee Inc</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>Raleigh, NC, US USA</t>
         </is>
       </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
@@ -1448,25 +1448,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Par Pacific Holdings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Platform Engineer - CDE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e82084d20e9979</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f4b90394ec3735</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=13e82084d20e9979</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Delta Dental Ins.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Cordova, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=f6f4b90394ec3735</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe7c58c72e83874</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI &amp; ML)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Software Development Engineer (AI &amp; ML)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>AI Scientist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Hoboken, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fe7c58c72e83874</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=28fad5a6eb6e90e7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Navitas</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
+          <t>https://www.indeed.com/viewjob?jk=04a71202b47b41de</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Application Integration Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Navitas</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010939cb7a520dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,77 +3016,77 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=010939cb7a520dc3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
         </is>
       </c>
     </row>
@@ -3098,152 +3098,152 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Developer Contractor</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Westford, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineers</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Activation Solution Engineer- TMT/CBS</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, HBase, Scala, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=fb564aaa33c98121</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Solutions Architect – Cloud Platforms</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>First Quality</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Automation &amp; Integration Developer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Professional Engineering Consultants</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f496e3f33567d8e1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Automation &amp; Integration Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Professional Engineering Consultants</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c144566d40a9779d</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,42 +5606,462 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer (contract)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>SQL/Power BI Developer</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>Intellibee Inc</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Raleigh, NC, US USA</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Data Fabric Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>KLA</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ann Arbor, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>RDS, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Power BI, Tableau, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98107848586892d4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G161"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud and Data Architect</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Technology Ventures</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Step Functions, S3, SQS, SNS, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=320c1faffbfddbde</t>
+          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,42 +1231,42 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Par Pacific Holdings</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba26fa47f7d9c017</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer - CDE</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Scala, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75b680abba58aa07</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
@@ -1798,25 +1798,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
@@ -2078,25 +2078,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13e82084d20e9979</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Delta Dental Ins.</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Rancho Cordova, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, ELT, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6f4b90394ec3735</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Engineer, Contract To Hire</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>66degrees</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI &amp; ML)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Scientist</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hoboken, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, Scala, MLOps, MLflow, CI/CD, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fe7c58c72e83874</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28fad5a6eb6e90e7</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04a71202b47b41de</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Application Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4202440469a7183f</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c336e57cb127fed</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer / Solutions Architect (Python &amp; GenAI)</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=620cef4cb61081c1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26-2239: QA Automation Engineer - Herndon, VA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Navitas</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d8f63f9ca803a56</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,207 +2806,207 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GCP Cloud Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=010939cb7a520dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SAP NS2 SuccessFactors Payroll Integration Expert and ABAP Professional</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3ecb94f6f318e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer Contractor</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westford, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, Data Modeling, ETL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a3da1ae20db072</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineers</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, MySQL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3983abcf47563a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Activation Solution Engineer- TMT/CBS</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, HBase, Scala, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb564aaa33c98121</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Automation &amp; Integration Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Professional Engineering Consultants</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f496e3f33567d8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Automation &amp; Integration Developer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Professional Engineering Consultants</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, MongoDB, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c144566d40a9779d</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Solutions Architect – Cloud Platforms</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>First Quality</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,637 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Wells Fargo</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Data Fabric Engineer</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>KLA</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Ann Arbor, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>RDS, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, Power BI, Tableau, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=98107848586892d4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,59 +2736,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,40 +5396,75 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
           <t>SQL/Power BI Developer</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B144" t="inlineStr">
         <is>
           <t>Intellibee Inc</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>Raleigh, NC, US USA</t>
         </is>
       </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer, Selling Partner Insights and Analytics</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=60a9c799766b00e5</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer, Contract To Hire</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>66degrees</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=329c33a2110e2ffd</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>PingOne</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,77 +2761,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bda7a0dc088567f8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,40 +5431,145 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Solutions Architect – Cloud Platforms</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>First Quality</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>PA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
           <t>SQL/Power BI Developer</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>Intellibee Inc</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>Raleigh, NC, US USA</t>
         </is>
       </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
         <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -1313,7 +1313,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer, Selling Partner Insights and Analytics</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Hadoop</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60a9c799766b00e5</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,24 +2691,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>PingOne</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=bda7a0dc088567f8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PingOne</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda7a0dc088567f8</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,59 +2841,59 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Enterprise Architecture</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Jade Global</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
@@ -1908,12 +1908,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Klaxontech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Robstown, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Traackr</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Quality Systems Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>North Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Spark, PySpark, Scala, Snowflake, NoSQL, Kimball, CI/CD, Git</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53641572c239d14d</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,87 +1238,87 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=5b50d646719ae69f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
@@ -1546,94 +1546,94 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Enterprise Architecture</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jade Global</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e941d3599cccbbd</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Klaxontech</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Robstown, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Databricks, GCP, Dataflow, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c444110ccacb047</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b35bb2b1b88eaf23</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Traackr</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c39424195effb79e</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,94 +2176,94 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,24 +2271,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quality Systems Specialist</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>North Charleston, SC, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de68c165b26c648e</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PingOne</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,112 +2726,112 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda7a0dc088567f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Darlington, SC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Hadoop, HDFS, Hive, Spark, Scala, NoSQL, ETL, Talend, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=cf54a52241c9ab8c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
@@ -5537,41 +5537,6 @@
       <c r="G146" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=295bf747ca0fd10d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G146"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Senior Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,137 +2176,137 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tremco CPG Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Beachwood, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,112 +2341,112 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>TD SYNNEX</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Investment Compliance Engineeer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Apollo</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddc1d55011d65dd</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Cloud Infrastructure Engineer Prin</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dayforce</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,94 +2841,94 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Darlington, SC, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Hive, Spark, Scala, NoSQL, ETL, Talend, Python</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf54a52241c9ab8c</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Solutions Architect – Cloud Platforms</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>First Quality</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Databricks, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,112 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3775b7c2910e4187</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ally Financial</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lewisville, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G149"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,172 +1161,172 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Devops engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=15ea8087038a49ef</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1000bfb92ccaf8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b50d646719ae69f</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>Vibrant Emotional Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,277 +1441,277 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>16.7</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5b50d646719ae69f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Database Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dimensional Fund Advisors</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer, Data (Remote, US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Renew home</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
+          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,137 +1721,137 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Associate, Software Engineering: Java</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,242 +1931,242 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tremco CPG Inc.</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Beachwood, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, SQL Server, MySQL, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b270e8c67c06f67</t>
+          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>MindCare Solutions Group</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Vanderbilt University</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Machine Learning Operations Trainee</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,137 +2351,137 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>TD SYNNEX</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.9</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Investment Compliance Engineeer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Apollo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cee8a0ae42d8d81</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer Prin</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dayforce</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Jenkins, Azure DevOps, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,242 +2631,242 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64ff20bb39da70f3</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,137 +2981,137 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,54 +3191,54 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>TD SYNNEX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3247,11 +3247,11 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,102 +3261,102 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,137 +3401,137 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,67 +3646,67 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Data Engineer/Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,67 +3751,67 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,42 +5606,1197 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Greenville, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Jackson, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Lincoln, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Boise, ID, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
           <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr">
+      <c r="B181" t="inlineStr">
         <is>
           <t>Ally Financial</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
+      <c r="C181" t="inlineStr">
         <is>
           <t>Lewisville, TX, US USA</t>
         </is>
       </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite Consultant</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G182"/>
+  <dimension ref="A1:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Steel Warehouse</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>South Bend, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
@@ -1728,17 +1728,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, Vertex AI, Spark</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
         </is>
       </c>
     </row>
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d5e6c69e5dcc101</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Platform &amp; Healthcare AI Analytics Engineer</t>
+          <t>Machine Learning Operations Trainee</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MindCare Solutions Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EMR, Athena, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=008f37aa6430130f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vanderbilt University</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, Data Modeling, dbt</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1c3ee64f59e29c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Trainee</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
+          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Associate, Software Engineering: Java</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,94 +2386,94 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
+          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a007da376997cdd6</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Data Ops Engineer (contract)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TD SYNNEX</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
+          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>TD SYNNEX</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,24 +3356,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,42 +3401,42 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer/Cloud Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Azure, Data Factory, Scala, Snowflake, Oracle, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c015dba2edf2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Python Developer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, ECS, Kafka, Data Modeling, ETL, ELT, Splunk, CI/CD, GitHub Actions, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f27e4c248823f3cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,24 +3916,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
@@ -4108,17 +4108,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>Senior Salesforce Developer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Alliant Insurance Services</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Site Reliability Engineer (contract)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,52 +6751,157 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Associate Engineer, AI Integration Analyst</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
           <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr">
+      <c r="B184" t="inlineStr">
         <is>
           <t>Openkyber</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
+      <c r="C184" t="inlineStr">
         <is>
           <t>GA, US USA</t>
         </is>
       </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
         <is>
           <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Junior DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,77 +1116,77 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Devops engineer</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ea8087038a49ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Devops engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1000bfb92ccaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=15ea8087038a49ef</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
+          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
+          <t>https://www.indeed.com/viewjob?jk=bb1000bfb92ccaf8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, GCP, Vertex AI, Scala, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
+          <t>https://www.indeed.com/viewjob?jk=f6b1e3ef5375d97c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c340175ff6347ecd</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8c32e2d7049ff2</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Ops Engineer (contract)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=856a0021ec6b2858</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Fintech</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
         </is>
       </c>
     </row>
@@ -3023,17 +3023,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,69 +3041,69 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TD SYNNEX</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TD SYNNEX</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,24 +3356,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,42 +3401,42 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
@@ -4493,17 +4493,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer (contract)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7241100643e3426</t>
+          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Associate Engineer, AI Integration Analyst</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Winston-Salem, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Short Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
+          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Shreveport, LA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
+          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
+          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Shreveport, LA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
+          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
+          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
+          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
+          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
+          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
+          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
+          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
+          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
+          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
+          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
+          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
+          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
+          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
+          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
+          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
+          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
+          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
+          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
+          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
+          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
+          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
+          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
+          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
+          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
+          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
+          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
+          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
+          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
+          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
+          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
+          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
+          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
+          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,34 +6786,34 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,24 +6821,24 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SAP Integration Suite Consultant</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6865,41 +6865,6 @@
         </is>
       </c>
       <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Junior DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS, Snowflake, Pyspark, SQL)</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, S3, RDS, Azure, Data Factory, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1309e7e5905e9f12</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Steel Warehouse</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>South Bend, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71eb13352e5c1a32</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data (Remote, US)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Renew home</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,77 +1606,77 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, GCP, Hadoop, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=690427c84612c68c</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, Vertex AI, Spark</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695bee5a222f3154</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Machine Learning Operations Trainee</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Senior Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Trainee</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
+          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Associate, Software Engineering: Java</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,49 +2316,49 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Snowflake, Oracle, ETL, ELT, Jenkins</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6da4932fc26ff43a</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer - Fintech</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=032692b6447e846b</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,69 +3041,69 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>TD SYNNEX</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Scala, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61b491dcf119f</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9781423ded3fa2b</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,42 +3391,42 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, Hive, Snowflake, Oracle, PostgreSQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dc4b4a6a2ce3590</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Development Security Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Dittman Incentive Marketing</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a1e98c36756d0852</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=333e8b31f084f577</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,42 +3846,42 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01307abdca065f19</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Salesforce Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Alliant Insurance Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09d7442a9096d240</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416a8506d47b063</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Contract Associate Development Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Sinclair Broadcast Group</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Winston-Salem, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebc95dd2bea57493</t>
+          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Short Hills, NJ, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb073e263cd375ad</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a42c4ea9e743558</t>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,2150 +4721,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7969caab4fdc3fd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a131bdccd5dfe683</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39a2def4665f0868</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Shreveport, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90a6aee373b7932a</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30db15ed7ce739d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c8e8d4ff04dcc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>St. Louis, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d32e3dabc3defd49</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4890395a6efa72de</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df3b5d307d35a646</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7874ab9a4b1ddb37</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d2b612f9a00d413</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76704cec11281802</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8fc3f27500c9a399</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Orlando, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bb4d62734b0505b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=710e43de726284cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35818880da2b7e5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f66fb3899c84c08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6950fff73368dd0</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=362db613a9d46a6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557986231199559a</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>New Orleans, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c12321bfdc84d51</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Oklahoma City, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b82133b39b7c0b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Montvale, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c167b1d4b68a3e22</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Memphis, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=02f0a7c0b03f5014</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=878f88f973ba3d5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2027cf85152f63f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=75e78e02407d6359</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfbd6e67d3fd8cfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Boulder, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=701baf4cf0f8fe9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcfe6c3637b19aa</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c92229dbb009cb6</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Des Moines, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5df6a1034f8d11</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Kansas City, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd2f8d8bdebb9bc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0fab502088647eba</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a336179fadc6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6739adde8d9aa7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f9762e0a7c4f2d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae8e30d2f5aa08d</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f21f7c72d92d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a94c8a15efcf12a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Jackson, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44d167f185224ba1</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Lincoln, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dda52628551ebad5</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12863926a8f4062f</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e34477bf322ef9e</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Cleveland, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aefe432545c06aad</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Knoxville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=951faf7271cbfa9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Grand Rapids, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2e5755edc6a6951c</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37b548052deb3ab1</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aea06ae53f170835</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Hartford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac9434a297d22bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74637e7a09c2131d</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ddbe6ce43611a92</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Boise, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=203fc2d7ad7bf6af</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=733b00ba9fecb840</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7dcb79cc790a91</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadd6b812c6f0dd0</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Bentonville, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe67800133c98286</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=722ea734bc204ae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Associate Engineer, AI Integration Analyst</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>KPMG</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4bb35373b469bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Ally Financial</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Junior DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,52 +1466,52 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b50d646719ae69f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Platform Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dimensional Fund Advisors</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=385c9a79fc872802</t>
+          <t>https://www.indeed.com/viewjob?jk=5b50d646719ae69f</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,42 +1616,42 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cd8c53893a5ad46</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf1c34ee91c952e8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=ae5ba63dac769db2</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911af4a079b795bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Machine Learning Operations Trainee</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Trainee</t>
+          <t>Senior Associate, Software Engineering: Java</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Options Clearing Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Associate, Software Engineering: Java</t>
+          <t>CrowdStrike Charlotte AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
+          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,24 +2796,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Software Development Engineer (AI &amp; ML)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Ridgefield, CT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Development Security Operations Engineer</t>
+          <t>Junior Cloud Security Analyst</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dittman Incentive Marketing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1e98c36756d0852</t>
+          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>Functional Construction Automation Data Analyst Specialist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Bechtel</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f7a44142b4858b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,15 +3558,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,59 +3576,59 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Development Security Operations Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Dittman Incentive Marketing</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>New Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=a1e98c36756d0852</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,42 +3881,42 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>PingOne</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,15 +3978,15 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,129 +3996,129 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=bda7a0dc088567f8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer (Python ETL)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Varteq</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, ETL, Docker, Airflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=805875ce39161cef</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>MuleSoft Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+          <t>https://www.indeed.com/viewjob?jk=87bb3ba8aec761d6</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Contract Associate Development Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c556a8e96adfe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Analyst - Business Intelligence</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ally Financial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lewisville, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SAP Integration Suite Consultant</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,14 +4696,14 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,15 +4721,330 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
+          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Analyst - Business Intelligence</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ally Financial</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Lewisville, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite Consultant</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Junior DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>

--- a/results/job_matches_2026-03-31.xlsx
+++ b/results/job_matches_2026-03-31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G132"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Digipulse Technologies Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, Athena, S3, SQS, SNS, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcb5051399e08706</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5a21d896e67e9f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Digipulse Technologies Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lansing, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Kinesis, Athena, S3, SQS, SNS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f98b55439904bef</t>
+          <t>https://www.indeed.com/viewjob?jk=dcb5051399e08706</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lansing, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8d675a6d5bcaeac</t>
+          <t>https://www.indeed.com/viewjob?jk=3f98b55439904bef</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45e9be9ee46290f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d8d675a6d5bcaeac</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a365abdf57475b3</t>
+          <t>https://www.indeed.com/viewjob?jk=45e9be9ee46290f1</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230910c469de2d76</t>
+          <t>https://www.indeed.com/viewjob?jk=4a365abdf57475b3</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c24bfaec7c9da6f</t>
+          <t>https://www.indeed.com/viewjob?jk=230910c469de2d76</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=451f37250ad0deac</t>
+          <t>https://www.indeed.com/viewjob?jk=7c24bfaec7c9da6f</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95355c1d74b312f</t>
+          <t>https://www.indeed.com/viewjob?jk=451f37250ad0deac</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3843d714f27ed59</t>
+          <t>https://www.indeed.com/viewjob?jk=b95355c1d74b312f</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78c7318f2c1862c3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3843d714f27ed59</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f462652eeb816d</t>
+          <t>https://www.indeed.com/viewjob?jk=78c7318f2c1862c3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7700cc8c2471209c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f462652eeb816d</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9808c47b5c4db28f</t>
+          <t>https://www.indeed.com/viewjob?jk=7700cc8c2471209c</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7306270caf1d6506</t>
+          <t>https://www.indeed.com/viewjob?jk=9808c47b5c4db28f</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a47090faeee0433</t>
+          <t>https://www.indeed.com/viewjob?jk=7306270caf1d6506</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58422662e905e73b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a47090faeee0433</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51a7cffbc3607a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=58422662e905e73b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
+          <t>https://www.indeed.com/viewjob?jk=51a7cffbc3607a3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer (AWS / Azure / GCP | Python | PySpark | ETL Pipelines)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,77 +1151,77 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, SNS, RDS, Azure</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
+          <t>https://www.indeed.com/viewjob?jk=48f31b0f83baadba</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer, Machine Learning</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point72</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b345815d3082c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Devops engineer</t>
+          <t>Software Engineer, Machine Learning</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Point72</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Data Modeling</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, RDS, BigQuery, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ea8087038a49ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5e09c185db263f81</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Devops engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb1000bfb92ccaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=15ea8087038a49ef</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Solution Developer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=e23577992da94237</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MDM Developer - Reltio and Informatica</t>
+          <t>Senior Data Solution Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
+          <t>https://www.indeed.com/viewjob?jk=60636b00b0503b4f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Development Engineer II - SQL/Python (Onsite)</t>
+          <t>MDM Developer - Reltio and Informatica</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tyson Foods Incorporated</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Springdale, AR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, API Gateway, IAM, RDS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
+          <t>https://www.indeed.com/viewjob?jk=62f00301c3deac9a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Development Engineer II - SQL/Python (Onsite)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyson Foods Incorporated</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Springdale, AR, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Kafka, Snowflake, Kimball</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
+          <t>https://www.indeed.com/viewjob?jk=1134e3a24fcb227f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b50d646719ae69f</t>
+          <t>https://www.indeed.com/viewjob?jk=b9ef3e482c1ec706</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Live Nation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Medallion Architecture, Hadoop, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
+          <t>https://www.indeed.com/viewjob?jk=4f5a1d94cdd22147</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer III- Python / Data Lake</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Hadoop</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
+          <t>https://www.indeed.com/viewjob?jk=ab05fb1efeca7401</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III- Python / Data Lake</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mj holding</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bridgeview, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Kinesis, Step Functions, RDS, Databricks, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b49f09d70a8053</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mj holding</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bridgeview, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
+          <t>https://www.indeed.com/viewjob?jk=607b114c3a54e137</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c88842d38c51c3e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Administrator</t>
+          <t>Amazon Contact Center Expert</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hartford, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
+          <t>https://www.indeed.com/viewjob?jk=f00b2d3ae1dd9c48</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Amazon Contact Center Expert</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, RDS, Google Cloud Platform, Vertex AI, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=104e155ccf64e907</t>
+          <t>https://www.indeed.com/viewjob?jk=4739a328dd61122e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
+          <t>https://www.indeed.com/viewjob?jk=c741b2b5bf35e58d</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c1b121d67d1c29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
+          <t>https://www.indeed.com/viewjob?jk=40aaa75b2184c0c1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Falcon Fusion Automation Engineer</t>
+          <t>Databricks Administrator</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Hartford, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,14 +1966,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
+          <t>https://www.indeed.com/viewjob?jk=41fcb22e7e1be3af</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Intelligence Advisory Specialist</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
+          <t>https://www.indeed.com/viewjob?jk=4cfe65132a8bf749</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data and AI Platform</t>
+          <t>Falcon Fusion Automation Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
+          <t>https://www.indeed.com/viewjob?jk=e915580476d1117f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Intelligence Advisory Specialist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5c368ca320721350</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer Advisor</t>
+          <t>Senior Data Engineer - Data and AI Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a485d3680b15c7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, Snowflake Schema</t>
+          <t>AWS, EMR, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca690758b1fe12cc</t>
+          <t>https://www.indeed.com/viewjob?jk=71c7ef21d9f323bb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Trainee</t>
+          <t>Cloud Solutions Engineer Advisor</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Splunk, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7ade899645b061</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed5b36af60806a7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Associate, Software Engineering: Java</t>
+          <t>Data Governance &amp; AI Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Options Clearing Corporation</t>
+          <t>Clean Harbors</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Norwell, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, IAM, RDS, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee8848102ba438f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>Software Engineer Specialist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26b7ea188aaaa21f</t>
+          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Governance &amp; AI Architect</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clean Harbors</t>
+          <t>Wavicle Data Solutions</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norwell, MA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c9ed46a79df142</t>
+          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a1da206e83b34e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineering Architect</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wavicle Data Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Azure, Data Factory, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da6f6c7407781883</t>
+          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53a21eb645f70762</t>
+          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>SAP Analytics Cloud Consultant</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef91196b68620667</t>
+          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SAP Analytics Cloud Consultant</t>
+          <t>Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13d26fcfc2d4f3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (contract)</t>
+          <t>Assoc AI Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Medline Industries</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Google Cloud Platform, GCP, HDFS, Spark, PySpark, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=377d8cfc7fa57208</t>
+          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Assoc AI Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Medline Industries</t>
+          <t>Slide Insurance</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Azure Cosmos DB, ETL, ELT</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1694de66666ce5ae</t>
+          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Slide Insurance</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Blob Storage, Google Cloud Platform, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=581ccabe792e3e2e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>mPulse Mobile</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127ec4f2c3b2c16c</t>
+          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>CrowdStrike Automation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e81ba3eb856803b</t>
+          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior AI Data Pipeline Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Trimble</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lake Oswego, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, ETL, MLOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d56a2eec25a4cdf1</t>
+          <t>https://www.indeed.com/viewjob?jk=590a2d7ae67854f1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>The Consortium Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cf3b9b1688cd663</t>
+          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CrowdStrike Automation Engineer</t>
+          <t>DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b86af2c91eec1e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Temp to Permanent - Redshift Dynamo data analytics AI subject matter expert senior data engineer.</t>
+          <t>GCP ETL Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>The Consortium Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, SQS, SNS, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d3155a48b630529</t>
+          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, Data Modeling, ETL, CI/CD</t>
+          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4d36b18dcbcb92</t>
+          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GCP ETL Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=918ab93ff3c3e435</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>Advisor IT Technology Analyst</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Puget Sound Energy</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Bothell, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>S3, IAM, RDS, Google Cloud Platform, GCP, Spark, PySpark, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9252404f1fd54bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ae612c56e0f980</t>
+          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer Document Intelligence</t>
+          <t>Senior Backend Engineer - Java</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
+          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
+          <t>https://www.indeed.com/viewjob?jk=89836d7fbc6b3c28</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Java</t>
+          <t>Senior Machine Learning Engineer Document Intelligence</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314171c69decc803</t>
+          <t>https://www.indeed.com/viewjob?jk=41276bf572b998e9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Development Engineer (AI &amp; ML)</t>
+          <t>GCP Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cbedcfe75811422</t>
+          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GCP Cloud Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fairway Independent Mortgage</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4956c23a03f89aba</t>
+          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps Engineer II – AWS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>HCSS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Kafka, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, DynamoDB, CI/CD, GitHub Actions, CodeBuild</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f45ba0b2e434ebdf</t>
+          <t>https://www.indeed.com/viewjob?jk=2c2c066ac730476f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Advisor IT Technology Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Puget Sound Energy</t>
+          <t>Premistar</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bothell, WA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, Azure, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=730de253e4e2fdc4</t>
+          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS CLOUD DATA / SOLUTION ARCHITECHT</t>
+          <t>Data integration Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ridgefield, CT, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dabf2b647f36e98c</t>
+          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Analyst - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fairway Independent Mortgage</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2030f383d0c07709</t>
+          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Cloud Administrator</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Premistar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Spark, PySpark, SQL Server, Data Modeling, Star Schema</t>
+          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b51ff213f12431eb</t>
+          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data integration Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB</t>
+          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3525ed6d9ad48128</t>
+          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Data Analyst - Remote</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Otelier</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aeaed27b6eac7dfe</t>
+          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GCP Cloud Administrator</t>
+          <t>PingOne Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>HI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>S3, Google Cloud Platform, GCP, Cloud Storage, HDFS, Spark, PySpark, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9066bd24bfd121ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior Cloud Security Analyst</t>
+          <t>CrowdStrike AI Security Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3422,11 +3422,11 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Blob Storage, Google Cloud Platform, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07a8b6c69b56ae04</t>
+          <t>https://www.indeed.com/viewjob?jk=5b6d920c4c2bd57b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Functional Construction Automation Data Analyst Specialist</t>
+          <t>ML Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Bechtel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f7a44142b4858b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>BI Engineer I (Remote)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEUMO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fort Wayne, IN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Azure, Data Factory, Scala, Snowflake, MLOps, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2960acef5cf8f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Otelier</t>
+          <t>TIAA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Scala, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=938af04f07a7b8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PingOne Cloud Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3558,15 +3558,15 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HI, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, SQL Server, ETL, Jenkins, Maven, Docker</t>
+          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d1bb860adb845b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Development Security Operations Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dittman Incentive Marketing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New Brunswick, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1e98c36756d0852</t>
+          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ML Platform Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a75d763e98635f6</t>
+          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BI Engineer I (Remote)</t>
+          <t>ADAS Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>NEUMO</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Fort Wayne, IN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ca11c463bffab2e</t>
+          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TIAA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Kafka, Snowflake, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c69ae1a5bbb91ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, Spark, PySpark, Scala, CI/CD, GitHub Actions, Terraform, Airflow</t>
+          <t>AWS, S3, API Gateway, ECS, Scala, PostgreSQL, DynamoDB, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e116a527e5005300</t>
+          <t>https://www.indeed.com/viewjob?jk=1dd7d3804967d98b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Everbridge</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbc0ffee81b18319</t>
+          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Full Stack Developer - Rental Platforms</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=250bf6d2d77f9c31</t>
+          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ADAS Cloud Infrastructure Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>BWE</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,77 +3846,77 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Databricks, GCP, Dataflow, Vertex AI, Spark, PySpark, NoSQL, MLOps, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=853124ce219322e0</t>
+          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Hadoop, HDFS, Spark, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccb8528012c6918c</t>
+          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DevOps Engineer II (CI/CD)</t>
+          <t>Senior Python Software Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jamf</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d081a2acf87111</t>
+          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,137 +3961,137 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efab53243a65d22c</t>
+          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PingOne</t>
+          <t>Business Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Publix</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lakeland, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Docker</t>
+          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda7a0dc088567f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Everbridge</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39df958f522b2b54</t>
+          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Full Stack Developer - Rental Platforms</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, DynamoDB</t>
+          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ecbf4be0e4e22122</t>
+          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>BWE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Dataflow, Scala, Snowflake, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=596f6e15cd38e69a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer 2, Customer Insights Delivery (Hybrid - Seattle, WA)</t>
+          <t>Full Stack/Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Spark, Scala, Kafka, Data Modeling, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a635d8f5dd2e2e8</t>
+          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Python Software Engineer</t>
+          <t>Data Engineer II (BI/ETL FOCUS)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>PerfectRx</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Azure DevOps, pytest</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db506ee21362577a</t>
+          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer (Python ETL)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Varteq</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, ETL, Docker, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86cd032741a613b</t>
+          <t>https://www.indeed.com/viewjob?jk=805875ce39161cef</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Business Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Publix</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lakeland, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Blob Storage, Unity Catalog, Spark, PySpark, Snowflake, Oracle, SQL Server, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdfa6620e1363720</t>
+          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>CrowdStrike GenAI Security Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Spark, Scala, Kafka, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebf5fc4fe451b2a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9e3319c71421c45d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Scala, Data Modeling, MLOps, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74a86411c17f0279</t>
+          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfccd38b986bc26f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack/Cloud Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, Scala, Kafka, Splunk, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85601cb639533196</t>
+          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer II (BI/ETL FOCUS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PerfectRx</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83309a17d6efa3a</t>
+          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer (Python ETL)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Varteq</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, ETL, Docker, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805875ce39161cef</t>
+          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, ETL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f113b544cb63ec40</t>
+          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Python Snowflake Data Engineer - ONSITE</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MuleSoft Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, Oracle, SQL Server, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87bb3ba8aec761d6</t>
+          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Software Engineer III - DevOps Automation Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MLOps, CI/CD, Azure DevOps, Docker, Kubernetes, pytest, Git</t>
+          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633beb97f5f7ea31</t>
+          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer III - DevOps Automation Engineer</t>
+          <t>Python Snowflake Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, API Gateway, RDS, Databricks, Scala, Splunk, Jenkins, Jenkins</t>
+          <t>RDS, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=455fef009e54202e</t>
+          <t>https://www.indeed.com/viewjob?jk=21b75f05c8869eb9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Analyst - Business Intelligence</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ally Financial</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d5fa6d1ea20eaf4</t>
+          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>SAP Integration Suite Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,357 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11a9093c69bdd7f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Cloud Storage, ETL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4863cbc6b3d6b1cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bce8d3a8d3ff964</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df2a2ae9eaa9d1d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=671dcf3696b00c81</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40b5b3fbb27785d</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e7c3732c3afe771</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=132a7e83f5ef115c</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Senior Analyst - Business Intelligence</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Ally Financial</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Lewisville, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Hadoop, Scala, Snowflake, Oracle, dbt, Power BI, Git</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c90642397a66650c</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>SAP Integration Suite Consultant</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Scala, Snowflake, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=524dae0940b2e550</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Junior DevOps Engineer (GCP)</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35e0e8efd2412038</t>
         </is>
       </c>
     </row>
